--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10398,6 +10398,36 @@
         <v>391.66</v>
       </c>
       <c r="H332" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>406.04</v>
+      </c>
+      <c r="C333" t="n">
+        <v>396.97</v>
+      </c>
+      <c r="D333" t="n">
+        <v>382.37</v>
+      </c>
+      <c r="E333" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="F333" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="G333" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="H333" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10414,7 +10444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B341"/>
+  <dimension ref="A1:B342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13827,6 +13857,16 @@
       </c>
       <c r="B341" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -13995,28 +14035,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.127065047350586</v>
+        <v>-0.1301695770331772</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06279063848392308</v>
+        <v>0.06575683502299867</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85241672602276</v>
+        <v>2.859417204207686</v>
       </c>
       <c r="N2" t="n">
-        <v>13.37500096958882</v>
+        <v>13.41258408197672</v>
       </c>
       <c r="O2" t="n">
-        <v>3.657184842141401</v>
+        <v>3.662319494797897</v>
       </c>
       <c r="P2" t="n">
-        <v>414.5521010548143</v>
+        <v>414.5849133960659</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -14077,28 +14117,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08926602062077148</v>
+        <v>-0.09125433683238383</v>
       </c>
       <c r="J3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03233499992192568</v>
+        <v>0.03388790037970058</v>
       </c>
       <c r="M3" t="n">
-        <v>2.754164819140027</v>
+        <v>2.755822441593115</v>
       </c>
       <c r="N3" t="n">
-        <v>13.23501435519441</v>
+        <v>13.22709061966955</v>
       </c>
       <c r="O3" t="n">
-        <v>3.637995925670397</v>
+        <v>3.636906737829491</v>
       </c>
       <c r="P3" t="n">
-        <v>402.6275106981628</v>
+        <v>402.6485255753655</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -14159,28 +14199,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08881086978376401</v>
+        <v>-0.09153722613218644</v>
       </c>
       <c r="J4" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02786323520660616</v>
+        <v>0.02963320030072025</v>
       </c>
       <c r="M4" t="n">
-        <v>2.896994324787464</v>
+        <v>2.90255596111398</v>
       </c>
       <c r="N4" t="n">
-        <v>15.27312730477838</v>
+        <v>15.28717759312238</v>
       </c>
       <c r="O4" t="n">
-        <v>3.908084864070684</v>
+        <v>3.90988204337706</v>
       </c>
       <c r="P4" t="n">
-        <v>389.2300692066547</v>
+        <v>389.258884564865</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -14241,28 +14281,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.14342329748882</v>
+        <v>-0.1467270387793407</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K5" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08278001556712766</v>
+        <v>0.08629714642936492</v>
       </c>
       <c r="M5" t="n">
-        <v>2.800873780157953</v>
+        <v>2.809632323857355</v>
       </c>
       <c r="N5" t="n">
-        <v>12.64990632558938</v>
+        <v>12.69998752437414</v>
       </c>
       <c r="O5" t="n">
-        <v>3.556670679946258</v>
+        <v>3.563704185868146</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3263873098893</v>
+        <v>387.3613051550109</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14323,28 +14363,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09578788204656334</v>
+        <v>-0.09722338266266792</v>
       </c>
       <c r="J6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K6" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04465400640912875</v>
+        <v>0.04617513541820817</v>
       </c>
       <c r="M6" t="n">
-        <v>2.535929914555972</v>
+        <v>2.535374546942163</v>
       </c>
       <c r="N6" t="n">
-        <v>10.89485101809684</v>
+        <v>10.8786839344663</v>
       </c>
       <c r="O6" t="n">
-        <v>3.300734920907287</v>
+        <v>3.298284998975422</v>
       </c>
       <c r="P6" t="n">
-        <v>385.8021902785825</v>
+        <v>385.8173623467855</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14405,28 +14445,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.13785881780278</v>
+        <v>-0.1423240955394826</v>
       </c>
       <c r="J7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K7" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07053178200377652</v>
+        <v>0.07450375579374191</v>
       </c>
       <c r="M7" t="n">
-        <v>2.999216226984311</v>
+        <v>3.014745792158703</v>
       </c>
       <c r="N7" t="n">
-        <v>13.90012435443345</v>
+        <v>14.01934754340918</v>
       </c>
       <c r="O7" t="n">
-        <v>3.728287053652581</v>
+        <v>3.744241918387376</v>
       </c>
       <c r="P7" t="n">
-        <v>401.3977977305129</v>
+        <v>401.4449920664865</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14468,7 +14508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H332"/>
+  <dimension ref="A1:H333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28415,6 +28455,48 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-35.44070602562273,174.3949074045321</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-35.44121878553271,174.3954983211188</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-35.44167785635065,174.3961709218178</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-35.44206483562259,174.39692568080864</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-35.4423661165893,174.3977522247764</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-35.442693280410246,174.39856252030893</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0076/nzd0076.xlsx
+++ b/data/nzd0076/nzd0076.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H333"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10430,6 +10430,96 @@
       <c r="H333" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>406.86</v>
+      </c>
+      <c r="C334" t="n">
+        <v>395.4</v>
+      </c>
+      <c r="D334" t="n">
+        <v>382.39</v>
+      </c>
+      <c r="E334" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="F334" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="G334" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>408.24</v>
+      </c>
+      <c r="C335" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="D335" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="E335" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="F335" t="n">
+        <v>382.92</v>
+      </c>
+      <c r="G335" t="n">
+        <v>390.84</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>408.24</v>
+      </c>
+      <c r="C336" t="n">
+        <v>396.59</v>
+      </c>
+      <c r="D336" t="n">
+        <v>390.91</v>
+      </c>
+      <c r="E336" t="n">
+        <v>381.43</v>
+      </c>
+      <c r="F336" t="n">
+        <v>382.92</v>
+      </c>
+      <c r="G336" t="n">
+        <v>390.84</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -10444,7 +10534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B342"/>
+  <dimension ref="A1:B345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13867,6 +13957,36 @@
       </c>
       <c r="B342" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -14035,28 +14155,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1301695770331772</v>
+        <v>-0.1360723464922394</v>
       </c>
       <c r="J2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06575683502299867</v>
+        <v>0.07228575070801302</v>
       </c>
       <c r="M2" t="n">
-        <v>2.859417204207686</v>
+        <v>2.863137090446435</v>
       </c>
       <c r="N2" t="n">
-        <v>13.41258408197672</v>
+        <v>13.3916044485914</v>
       </c>
       <c r="O2" t="n">
-        <v>3.662319494797897</v>
+        <v>3.659454118935145</v>
       </c>
       <c r="P2" t="n">
-        <v>414.5849133960659</v>
+        <v>414.6475190942504</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -14117,28 +14237,28 @@
         <v>0.1349</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09125433683238383</v>
+        <v>-0.09840228817223423</v>
       </c>
       <c r="J3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K3" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03388790037970058</v>
+        <v>0.03955140705033777</v>
       </c>
       <c r="M3" t="n">
-        <v>2.755822441593115</v>
+        <v>2.766487308917223</v>
       </c>
       <c r="N3" t="n">
-        <v>13.22709061966955</v>
+        <v>13.25116050365905</v>
       </c>
       <c r="O3" t="n">
-        <v>3.636906737829491</v>
+        <v>3.640214348587051</v>
       </c>
       <c r="P3" t="n">
-        <v>402.6485255753655</v>
+        <v>402.7243407476648</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -14199,28 +14319,28 @@
         <v>0.0965</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09153722613218644</v>
+        <v>-0.09299356284807547</v>
       </c>
       <c r="J4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K4" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02963320030072025</v>
+        <v>0.03092273975487103</v>
       </c>
       <c r="M4" t="n">
-        <v>2.90255596111398</v>
+        <v>2.908812978829161</v>
       </c>
       <c r="N4" t="n">
-        <v>15.28717759312238</v>
+        <v>15.27276062237579</v>
       </c>
       <c r="O4" t="n">
-        <v>3.90988204337706</v>
+        <v>3.908037950477937</v>
       </c>
       <c r="P4" t="n">
-        <v>389.258884564865</v>
+        <v>389.2742830237258</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -14281,28 +14401,28 @@
         <v>0.08409999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1467270387793407</v>
+        <v>-0.1519643823977051</v>
       </c>
       <c r="J5" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K5" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08629714642936492</v>
+        <v>0.09309837634201845</v>
       </c>
       <c r="M5" t="n">
-        <v>2.809632323857355</v>
+        <v>2.812466300057711</v>
       </c>
       <c r="N5" t="n">
-        <v>12.69998752437414</v>
+        <v>12.67748264568231</v>
       </c>
       <c r="O5" t="n">
-        <v>3.563704185868146</v>
+        <v>3.560545273645921</v>
       </c>
       <c r="P5" t="n">
-        <v>387.3613051550109</v>
+        <v>387.4168438295858</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -14363,28 +14483,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09722338266266792</v>
+        <v>-0.0993598668964457</v>
       </c>
       <c r="J6" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K6" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04617513541820817</v>
+        <v>0.04895290274193842</v>
       </c>
       <c r="M6" t="n">
-        <v>2.535374546942163</v>
+        <v>2.5230791255546</v>
       </c>
       <c r="N6" t="n">
-        <v>10.8786839344663</v>
+        <v>10.80878580748767</v>
       </c>
       <c r="O6" t="n">
-        <v>3.298284998975422</v>
+        <v>3.287671791327059</v>
       </c>
       <c r="P6" t="n">
-        <v>385.8173623467855</v>
+        <v>385.8400091656898</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -14445,28 +14565,28 @@
         <v>0.0856</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1423240955394826</v>
+        <v>-0.1557237431996772</v>
       </c>
       <c r="J7" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K7" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07450375579374191</v>
+        <v>0.08670798502963162</v>
       </c>
       <c r="M7" t="n">
-        <v>3.014745792158703</v>
+        <v>3.062352045621759</v>
       </c>
       <c r="N7" t="n">
-        <v>14.01934754340918</v>
+        <v>14.39433377840453</v>
       </c>
       <c r="O7" t="n">
-        <v>3.744241918387376</v>
+        <v>3.793986528495394</v>
       </c>
       <c r="P7" t="n">
-        <v>401.4449920664865</v>
+        <v>401.5871164353773</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -14508,7 +14628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H333"/>
+  <dimension ref="A1:H336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28497,6 +28617,132 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-35.44070032547628,174.3949131560947</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-35.44123048571932,174.39548858914918</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-35.441677698345536,174.39617102794261</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-35.442060501898375,174.3969283905132</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-35.442371633392455,174.3977484808004</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-35.442706273666914,174.39855238320013</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-35.4406907325463,174.39492283555194</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-35.44122161742508,174.39549596561048</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-35.44165992276806,174.3961829669807</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-35.44203770971821,174.39694264154733</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-35.44235003904807,174.39776313578938</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-35.44268963318016,174.39856536581257</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-35.4406907325463,174.39492283555194</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-35.44122161742508,174.39549596561048</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-35.44161038815298,174.3962162370729</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-35.44203770971821,174.39694264154733</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-35.44235003904807,174.39776313578938</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-35.44268963318016,174.39856536581257</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
